--- a/design/关卡表.xlsx
+++ b/design/关卡表.xlsx
@@ -100,7 +100,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -117,11 +117,341 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/comments/fieldNotes2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 Map 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿是历史阅读副本，正式地图读取地图表.xlsx。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+旧设计区分 1=灰盒清怪、2=撤离模式。本工作簿保留历史地图内容，未作为当前正式地图来源。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+地图边界尺寸，单位为毫米，1000 毫米=1 米。地图横向为 [0, Width]、纵向为 [0, Height]，碰撞与出生需在边界内。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+地图边界尺寸，单位为毫米，1000 毫米=1 米。地图横向为 [0, Width]、纵向为 [0, Height]，碰撞与出生需在边界内。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+每 Tick 向下增加的速度幅值，单位为毫米/Tick²。固定 60 Tick/秒；它不是以秒为单位的重力加速度。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 MapSolid 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿是历史阅读副本，正式地图读取地图表.xlsx。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Map.MapIdx，决定该行属于哪张地图。地图、碰撞块、出生点的 ID 各自独立，不按数字位推断归属。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形左下角坐标，单位为毫米，X 向右、Y 向上。区域右上角为 (X+W, Y+H)，须与出生点的脚底中心坐标区别。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形左下角坐标，单位为毫米，X 向右、Y 向上。区域右上角为 (X+W, Y+H)，须与出生点的脚底中心坐标区别。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形的宽或高，单位为毫米，必须为正数。与左下角 X、Y 共同定义区域，X+W、Y+H 不得超出地图边界。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形的宽或高，单位为毫米，必须为正数。与左下角 X、Y 共同定义区域，X+W、Y+H 不得超出地图边界。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+标识一个出生配置实例，与角色/怪物配置 ID 及运行时实体 ID 分开。多个出生点可以引用同一种角色配置；撤离条件引用怪物出生实例。本工作簿是历史阅读副本，正式地图读取地图表.xlsx。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Map.MapIdx，决定该行属于哪张地图。地图、碰撞块、出生点的 ID 各自独立，不按数字位推断归属。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Player.PlayerIdx，选择角色基础配置。此 ID 不表示本局玩家实体，也不使用名称作为关联键。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Equip.ItemIdx，再通过 Equip.WeaponIdx 找到枪械配置。此处填写装备物品 ID，不直接填写 WeaponIdx。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+出生位置使用脚底中心坐标，单位为毫米，X 向右、Y 向上。不能将其当作碰撞矩形左下角，检查出生空间时还需计入角色宽高。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+出生位置使用脚底中心坐标，单位为毫米，X 向右、Y 向上。不能将其当作碰撞矩形左下角，检查出生空间时还需计入角色宽高。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+标识一个出生配置实例，与角色/怪物配置 ID 及运行时实体 ID 分开。多个出生点可以引用同一种角色配置；撤离条件引用怪物出生实例。本工作簿是历史阅读副本，正式地图读取地图表.xlsx。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Map.MapIdx，决定该行属于哪张地图。地图、碰撞块、出生点的 ID 各自独立，不按数字位推断归属。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Monster.MonsterIdx，选择怪物基础配置。同一种怪物可由多个不同 SpawnIdx 的出生点生成。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+出生位置使用脚底中心坐标，单位为毫米，X 向右、Y 向上。不能将其当作碰撞矩形左下角，检查出生空间时还需计入角色宽高。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+出生位置使用脚底中心坐标，单位为毫米，X 向右、Y 向上。不能将其当作碰撞矩形左下角，检查出生空间时还需计入角色宽高。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+怪物脚底中心的巡逻左端 X 坐标，单位为毫米。须与 PatrolMax 组成有效区间，并为怪物半宽及连续地面支撑留出空间。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+怪物脚底中心的巡逻右端 X 坐标，单位为毫米。不得小于 PatrolMin；整个巡逻区域需避免穿墙、悬空和越界。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 ExtractPoint 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿是历史阅读副本，正式地图读取地图表.xlsx。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Map.MapIdx，决定该行属于哪张地图。地图、碰撞块、出生点的 ID 各自独立，不按数字位推断归属。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形左下角坐标，单位为毫米，X 向右、Y 向上。区域右上角为 (X+W, Y+H)，须与出生点的脚底中心坐标区别。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形左下角坐标，单位为毫米，X 向右、Y 向上。区域右上角为 (X+W, Y+H)，须与出生点的脚底中心坐标区别。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形的宽或高，单位为毫米，必须为正数。与左下角 X、Y 共同定义区域，X+W、Y+H 不得超出地图边界。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形的宽或高，单位为毫米，必须为正数。与左下角 X、Y 共同定义区域，X+W、Y+H 不得超出地图边界。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+进入撤离区后需要连续保持的 Tick 数，60 Tick=1 秒。离开区域、受到正伤害或死亡会清零，暂停冻结计时。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用同地图 MonsterSpawn.SpawnIdx，指定要击败的具体 Boss 出生实例，不是 MonsterIdx。此历史副本保留旧的 Rank=2 为 Boss、0 为无 Boss 条件的设计；当前正式配置须以地图表和实际校验为准。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -360,118 +690,118 @@
       <x:c r="I3" s="2"/>
     </x:row>
     <x:row r="5" ht="29" customHeight="1">
-      <x:c r="A5" s="5" t="str">
+      <x:c r="A5" s="16" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="B5" s="16" t="str">
         <x:v>名称</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="str">
+      <x:c r="C5" s="16" t="str">
         <x:v>模式</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="str">
+      <x:c r="D5" s="16" t="str">
         <x:v>宽度</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="str">
+      <x:c r="E5" s="16" t="str">
         <x:v>高度</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="str">
+      <x:c r="F5" s="16" t="str">
         <x:v>碰撞块数</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="str">
+      <x:c r="G5" s="16" t="str">
         <x:v>玩家出生数</x:v>
       </x:c>
-      <x:c r="H5" s="5" t="str">
+      <x:c r="H5" s="16" t="str">
         <x:v>怪物出生数</x:v>
       </x:c>
-      <x:c r="I5" s="5" t="str">
+      <x:c r="I5" s="16" t="str">
         <x:v>撤离点数</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="3" t="n">
+      <x:c r="A6" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="3" t="str">
+      <x:c r="B6" s="17" t="str">
         <x:v>原始灰盒</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="str">
+      <x:c r="C6" s="17" t="str">
         <x:v>灰盒清怪</x:v>
       </x:c>
-      <x:c r="D6" s="7" t="n">
+      <x:c r="D6" s="18" t="n">
         <x:v>24000</x:v>
       </x:c>
-      <x:c r="E6" s="7" t="n">
+      <x:c r="E6" s="18" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F6" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G6" s="7" t="n">
+      <x:c r="F6" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G6" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H6" s="7" t="n">
+      <x:c r="H6" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I6" s="7" t="n">
+      <x:c r="I6" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="6" t="n">
+      <x:c r="A7" s="19" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="str">
+      <x:c r="B7" s="19" t="str">
         <x:v>撤离演示（示例）</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C7" s="19" t="str">
         <x:v>撤离示例</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="n">
+      <x:c r="D7" s="20" t="n">
         <x:v>24000</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="n">
+      <x:c r="E7" s="20" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G7" s="8" t="n">
+      <x:c r="F7" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G7" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H7" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I7" s="8" t="n">
+      <x:c r="H7" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I7" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="str">
+      <x:c r="A8" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="str">
         <x:v>废弃工厂（初始）</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="str">
+      <x:c r="C8" s="17" t="str">
         <x:v>撤离示例</x:v>
       </x:c>
-      <x:c r="D8" s="7" t="n">
+      <x:c r="D8" s="18" t="n">
         <x:v>36000</x:v>
       </x:c>
-      <x:c r="E8" s="7" t="n">
+      <x:c r="E8" s="18" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="n">
+      <x:c r="F8" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G8" s="7" t="n">
+      <x:c r="G8" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H8" s="7" t="n">
+      <x:c r="H8" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="n">
+      <x:c r="I8" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -489,22 +819,22 @@
       <x:c r="I10" s="10"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="3" t="str">
+      <x:c r="A11" s="17" t="str">
         <x:v>提前出口</x:v>
       </x:c>
-      <x:c r="B11" s="3" t="str">
+      <x:c r="B11" s="17" t="str">
         <x:v>撤离点 2</x:v>
       </x:c>
-      <x:c r="C11" s="3" t="str">
+      <x:c r="C11" s="17" t="str">
         <x:v>X=14,000～16,000</x:v>
       </x:c>
-      <x:c r="D11" s="3" t="str">
+      <x:c r="D11" s="17" t="str">
         <x:v>Y=0～2,400</x:v>
       </x:c>
-      <x:c r="E11" s="3" t="str">
+      <x:c r="E11" s="17" t="str">
         <x:v>120 Tick</x:v>
       </x:c>
-      <x:c r="F11" s="3" t="str">
+      <x:c r="F11" s="17" t="str">
         <x:v>无需 Boss</x:v>
       </x:c>
       <x:c r="G11" s="3"/>
@@ -512,22 +842,22 @@
       <x:c r="I11" s="3"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="3" t="str">
+      <x:c r="A12" s="17" t="str">
         <x:v>首领出口</x:v>
       </x:c>
-      <x:c r="B12" s="3" t="str">
+      <x:c r="B12" s="17" t="str">
         <x:v>撤离点 3</x:v>
       </x:c>
-      <x:c r="C12" s="3" t="str">
+      <x:c r="C12" s="17" t="str">
         <x:v>X=34,200～35,700</x:v>
       </x:c>
-      <x:c r="D12" s="3" t="str">
+      <x:c r="D12" s="17" t="str">
         <x:v>Y=0～2,800</x:v>
       </x:c>
-      <x:c r="E12" s="3" t="str">
+      <x:c r="E12" s="17" t="str">
         <x:v>180 Tick</x:v>
       </x:c>
-      <x:c r="F12" s="3" t="str">
+      <x:c r="F12" s="17" t="str">
         <x:v>出生 25 死亡</x:v>
       </x:c>
       <x:c r="G12" s="3"/>
@@ -566,162 +896,163 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>名称</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>地图模式</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>地图宽度（毫米）</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>地图高度（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="16" t="str">
         <x:v>重力（毫米/Tick²）</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="16" t="str">
         <x:v>场景资源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="11" t="str">
+      <x:c r="A2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="21" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="G2" s="11" t="str">
+      <x:c r="C2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="G2" s="21" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="13" t="str">
+      <x:c r="A3" s="22" t="str">
         <x:v>MapIdx</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="22" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C3" s="13" t="str">
+      <x:c r="C3" s="22" t="str">
         <x:v>Mode</x:v>
       </x:c>
-      <x:c r="D3" s="13" t="str">
+      <x:c r="D3" s="22" t="str">
         <x:v>Width</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="str">
+      <x:c r="E3" s="22" t="str">
         <x:v>Height</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="str">
+      <x:c r="F3" s="22" t="str">
         <x:v>Gravity</x:v>
       </x:c>
-      <x:c r="G3" s="13" t="str">
+      <x:c r="G3" s="22" t="str">
         <x:v>SceneId</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="15" t="str">
+      <x:c r="A4" s="23" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="15" t="str">
+      <x:c r="B4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="G4" s="23" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
-      <x:c r="A5" s="7" t="n">
+      <x:c r="A5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="str">
+      <x:c r="B5" s="18" t="str">
         <x:v>原始灰盒</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="n">
+      <x:c r="C5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="n">
+      <x:c r="D5" s="18" t="n">
         <x:v>24000</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="n">
+      <x:c r="E5" s="18" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="n">
+      <x:c r="F5" s="18" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G5" s="7"/>
+      <x:c r="G5" s="18"/>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
-      <x:c r="A6" s="8" t="n">
+      <x:c r="A6" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="B6" s="20" t="str">
         <x:v>撤离演示（示例）</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="n">
+      <x:c r="C6" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="n">
+      <x:c r="D6" s="20" t="n">
         <x:v>24000</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="n">
+      <x:c r="E6" s="20" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="n">
+      <x:c r="F6" s="20" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G6" s="8"/>
+      <x:c r="G6" s="20"/>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
-      <x:c r="A7" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="str">
+      <x:c r="A7" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="18" t="str">
         <x:v>废弃工厂（初始）</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="n">
+      <x:c r="C7" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="7" t="n">
+      <x:c r="D7" s="18" t="n">
         <x:v>36000</x:v>
       </x:c>
-      <x:c r="E7" s="7" t="n">
+      <x:c r="E7" s="18" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="F7" s="7" t="n">
+      <x:c r="F7" s="18" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G7" s="7"/>
+      <x:c r="G7" s="18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -738,287 +1069,288 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>碰撞块ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>X（毫米）</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>Y（毫米）</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>宽（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="16" t="str">
         <x:v>高（毫米）</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="str">
+      <x:c r="A2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="21" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="13" t="str">
+      <x:c r="A3" s="22" t="str">
         <x:v>SolidIdx</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="22" t="str">
         <x:v>MapIdx</x:v>
       </x:c>
-      <x:c r="C3" s="13" t="str">
+      <x:c r="C3" s="22" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="D3" s="13" t="str">
+      <x:c r="D3" s="22" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="str">
+      <x:c r="E3" s="22" t="str">
         <x:v>W</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="str">
+      <x:c r="F3" s="22" t="str">
         <x:v>H</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="15" t="str">
+      <x:c r="A4" s="23" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="15" t="str">
+      <x:c r="B4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
-      <x:c r="A5" s="7" t="n">
+      <x:c r="A5" s="18" t="n">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="n">
+      <x:c r="B5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="n">
+      <x:c r="C5" s="18" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="n">
+      <x:c r="D5" s="18" t="n">
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="n">
+      <x:c r="E5" s="18" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="n">
+      <x:c r="F5" s="18" t="n">
         <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
-      <x:c r="A6" s="8" t="n">
+      <x:c r="A6" s="20" t="n">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="n">
+      <x:c r="B6" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="n">
+      <x:c r="C6" s="20" t="n">
         <x:v>8500</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="n">
+      <x:c r="D6" s="20" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="n">
+      <x:c r="E6" s="20" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="n">
+      <x:c r="F6" s="20" t="n">
         <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
-      <x:c r="A7" s="7" t="n">
+      <x:c r="A7" s="18" t="n">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="n">
+      <x:c r="B7" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="n">
+      <x:c r="C7" s="18" t="n">
         <x:v>15000</x:v>
       </x:c>
-      <x:c r="D7" s="7" t="n">
+      <x:c r="D7" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E7" s="7" t="n">
+      <x:c r="E7" s="18" t="n">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="F7" s="7" t="n">
+      <x:c r="F7" s="18" t="n">
         <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
-      <x:c r="A8" s="8" t="n">
+      <x:c r="A8" s="20" t="n">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="n">
+      <x:c r="B8" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="n">
+      <x:c r="C8" s="20" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="n">
+      <x:c r="D8" s="20" t="n">
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="n">
+      <x:c r="E8" s="20" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="n">
+      <x:c r="F8" s="20" t="n">
         <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
-      <x:c r="A9" s="7" t="n">
+      <x:c r="A9" s="18" t="n">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="n">
+      <x:c r="B9" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C9" s="7" t="n">
+      <x:c r="C9" s="18" t="n">
         <x:v>8500</x:v>
       </x:c>
-      <x:c r="D9" s="7" t="n">
+      <x:c r="D9" s="18" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="E9" s="7" t="n">
+      <x:c r="E9" s="18" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="F9" s="7" t="n">
+      <x:c r="F9" s="18" t="n">
         <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
-      <x:c r="A10" s="8" t="n">
+      <x:c r="A10" s="20" t="n">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="n">
+      <x:c r="B10" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C10" s="8" t="n">
+      <x:c r="C10" s="20" t="n">
         <x:v>15000</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="n">
+      <x:c r="D10" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="n">
+      <x:c r="E10" s="20" t="n">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="F10" s="8" t="n">
+      <x:c r="F10" s="20" t="n">
         <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
-      <x:c r="A11" s="7" t="n">
+      <x:c r="A11" s="18" t="n">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="n">
+      <x:c r="B11" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D11" s="7" t="n">
+      <x:c r="D11" s="18" t="n">
         <x:v>1400</x:v>
       </x:c>
-      <x:c r="E11" s="7" t="n">
+      <x:c r="E11" s="18" t="n">
         <x:v>2600</x:v>
       </x:c>
-      <x:c r="F11" s="7" t="n">
+      <x:c r="F11" s="18" t="n">
         <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
-      <x:c r="A12" s="8" t="n">
+      <x:c r="A12" s="20" t="n">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="B12" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="8" t="n">
+      <x:c r="B12" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="n">
         <x:v>11000</x:v>
       </x:c>
-      <x:c r="D12" s="8" t="n">
+      <x:c r="D12" s="20" t="n">
         <x:v>2600</x:v>
       </x:c>
-      <x:c r="E12" s="8" t="n">
+      <x:c r="E12" s="20" t="n">
         <x:v>2400</x:v>
       </x:c>
-      <x:c r="F12" s="8" t="n">
+      <x:c r="F12" s="20" t="n">
         <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
-      <x:c r="A13" s="7" t="n">
+      <x:c r="A13" s="18" t="n">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="B13" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="7" t="n">
+      <x:c r="B13" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="D13" s="7" t="n">
+      <x:c r="D13" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="7" t="n">
+      <x:c r="E13" s="18" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="F13" s="7" t="n">
+      <x:c r="F13" s="18" t="n">
         <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
-      <x:c r="A14" s="8" t="n">
+      <x:c r="A14" s="20" t="n">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="B14" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="8" t="n">
+      <x:c r="B14" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="n">
         <x:v>24500</x:v>
       </x:c>
-      <x:c r="D14" s="8" t="n">
+      <x:c r="D14" s="20" t="n">
         <x:v>1600</x:v>
       </x:c>
-      <x:c r="E14" s="8" t="n">
+      <x:c r="E14" s="20" t="n">
         <x:v>2500</x:v>
       </x:c>
-      <x:c r="F14" s="8" t="n">
+      <x:c r="F14" s="20" t="n">
         <x:v>400</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1035,147 +1367,148 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>玩家出生ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>玩家配置ID</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>初始装备道具ID</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>X（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="16" t="str">
         <x:v>Y（毫米）</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="str">
+      <x:c r="A2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="21" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="13" t="str">
+      <x:c r="A3" s="22" t="str">
         <x:v>SpawnIdx</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="22" t="str">
         <x:v>MapIdx</x:v>
       </x:c>
-      <x:c r="C3" s="13" t="str">
+      <x:c r="C3" s="22" t="str">
         <x:v>PlayerIdx</x:v>
       </x:c>
-      <x:c r="D3" s="13" t="str">
+      <x:c r="D3" s="22" t="str">
         <x:v>EquipItemIdx</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="str">
+      <x:c r="E3" s="22" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="str">
+      <x:c r="F3" s="22" t="str">
         <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="15" t="str">
+      <x:c r="A4" s="23" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="15" t="str">
+      <x:c r="B4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
-      <x:c r="A5" s="7" t="n">
+      <x:c r="A5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="n">
+      <x:c r="B5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="n">
+      <x:c r="C5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="n">
+      <x:c r="D5" s="18" t="n">
         <x:v>100000001</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="n">
+      <x:c r="E5" s="18" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="n">
+      <x:c r="F5" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
-      <x:c r="A6" s="8" t="n">
+      <x:c r="A6" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="n">
+      <x:c r="B6" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="n">
+      <x:c r="C6" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="n">
+      <x:c r="D6" s="20" t="n">
         <x:v>100000001</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="n">
+      <x:c r="E6" s="20" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="n">
+      <x:c r="F6" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
-      <x:c r="A7" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="7" t="n">
+      <x:c r="A7" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="n">
         <x:v>100000002</x:v>
       </x:c>
-      <x:c r="E7" s="7" t="n">
+      <x:c r="E7" s="18" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="F7" s="7" t="n">
+      <x:c r="F7" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1193,329 +1526,330 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>怪物出生ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>怪物配置ID</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>X（毫米）</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>Y（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="16" t="str">
         <x:v>巡逻左端（毫米）</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="16" t="str">
         <x:v>巡逻右端（毫米）</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="G2" s="11" t="str">
+      <x:c r="A2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="G2" s="21" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="13" t="str">
+      <x:c r="A3" s="22" t="str">
         <x:v>SpawnIdx</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="22" t="str">
         <x:v>MapIdx</x:v>
       </x:c>
-      <x:c r="C3" s="13" t="str">
+      <x:c r="C3" s="22" t="str">
         <x:v>MonsterIdx</x:v>
       </x:c>
-      <x:c r="D3" s="13" t="str">
+      <x:c r="D3" s="22" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="str">
+      <x:c r="E3" s="22" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="str">
+      <x:c r="F3" s="22" t="str">
         <x:v>PatrolMin</x:v>
       </x:c>
-      <x:c r="G3" s="13" t="str">
+      <x:c r="G3" s="22" t="str">
         <x:v>PatrolMax</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="15" t="str">
+      <x:c r="A4" s="23" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="15" t="str">
+      <x:c r="B4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="G4" s="23" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
-      <x:c r="A5" s="7" t="n">
+      <x:c r="A5" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="n">
+      <x:c r="B5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="n">
+      <x:c r="C5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="n">
+      <x:c r="D5" s="18" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="n">
+      <x:c r="E5" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="n">
+      <x:c r="F5" s="18" t="n">
         <x:v>11000</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="n">
+      <x:c r="G5" s="18" t="n">
         <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
-      <x:c r="A6" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="n">
+      <x:c r="A6" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="n">
+      <x:c r="C6" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="n">
+      <x:c r="D6" s="20" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="n">
+      <x:c r="E6" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="n">
+      <x:c r="F6" s="20" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="n">
+      <x:c r="G6" s="20" t="n">
         <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
-      <x:c r="A7" s="7" t="n">
+      <x:c r="A7" s="18" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="n">
+      <x:c r="B7" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="n">
+      <x:c r="C7" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="7" t="n">
+      <x:c r="D7" s="18" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="E7" s="7" t="n">
+      <x:c r="E7" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="7" t="n">
+      <x:c r="F7" s="18" t="n">
         <x:v>11000</x:v>
       </x:c>
-      <x:c r="G7" s="7" t="n">
+      <x:c r="G7" s="18" t="n">
         <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
-      <x:c r="A8" s="8" t="n">
+      <x:c r="A8" s="20" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="n">
+      <x:c r="B8" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="n">
+      <x:c r="C8" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="n">
+      <x:c r="D8" s="20" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="n">
+      <x:c r="E8" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="n">
+      <x:c r="F8" s="20" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="G8" s="8" t="n">
+      <x:c r="G8" s="20" t="n">
         <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
-      <x:c r="A9" s="7" t="n">
+      <x:c r="A9" s="18" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="n">
+      <x:c r="B9" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C9" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="7" t="n">
+      <x:c r="C9" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="n">
         <x:v>22800</x:v>
       </x:c>
-      <x:c r="E9" s="7" t="n">
+      <x:c r="E9" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F9" s="7" t="n">
+      <x:c r="F9" s="18" t="n">
         <x:v>21700</x:v>
       </x:c>
-      <x:c r="G9" s="7" t="n">
+      <x:c r="G9" s="18" t="n">
         <x:v>23200</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
-      <x:c r="A10" s="8" t="n">
+      <x:c r="A10" s="20" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="8" t="n">
+      <x:c r="B10" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="n">
+      <x:c r="D10" s="20" t="n">
         <x:v>8500</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="n">
+      <x:c r="E10" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="8" t="n">
+      <x:c r="F10" s="20" t="n">
         <x:v>7500</x:v>
       </x:c>
-      <x:c r="G10" s="8" t="n">
+      <x:c r="G10" s="20" t="n">
         <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
-      <x:c r="A11" s="7" t="n">
+      <x:c r="A11" s="18" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="n">
+      <x:c r="B11" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D11" s="7" t="n">
+      <x:c r="D11" s="18" t="n">
         <x:v>15000</x:v>
       </x:c>
-      <x:c r="E11" s="7" t="n">
+      <x:c r="E11" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="7" t="n">
+      <x:c r="F11" s="18" t="n">
         <x:v>14000</x:v>
       </x:c>
-      <x:c r="G11" s="7" t="n">
+      <x:c r="G11" s="18" t="n">
         <x:v>17000</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
-      <x:c r="A12" s="8" t="n">
+      <x:c r="A12" s="20" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B12" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="8" t="n">
+      <x:c r="B12" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D12" s="8" t="n">
+      <x:c r="D12" s="20" t="n">
         <x:v>22500</x:v>
       </x:c>
-      <x:c r="E12" s="8" t="n">
+      <x:c r="E12" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="8" t="n">
+      <x:c r="F12" s="20" t="n">
         <x:v>21000</x:v>
       </x:c>
-      <x:c r="G12" s="8" t="n">
+      <x:c r="G12" s="20" t="n">
         <x:v>23500</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
-      <x:c r="A13" s="7" t="n">
+      <x:c r="A13" s="18" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B13" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="7" t="n">
+      <x:c r="B13" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D13" s="7" t="n">
+      <x:c r="D13" s="18" t="n">
         <x:v>29500</x:v>
       </x:c>
-      <x:c r="E13" s="7" t="n">
+      <x:c r="E13" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="7" t="n">
+      <x:c r="F13" s="18" t="n">
         <x:v>28000</x:v>
       </x:c>
-      <x:c r="G13" s="7" t="n">
+      <x:c r="G13" s="18" t="n">
         <x:v>30900</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
-      <x:c r="A14" s="8" t="n">
+      <x:c r="A14" s="20" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B14" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="8" t="n">
+      <x:c r="B14" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D14" s="8" t="n">
+      <x:c r="D14" s="20" t="n">
         <x:v>33500</x:v>
       </x:c>
-      <x:c r="E14" s="8" t="n">
+      <x:c r="E14" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="8" t="n">
+      <x:c r="F14" s="20" t="n">
         <x:v>32500</x:v>
       </x:c>
-      <x:c r="G14" s="8" t="n">
+      <x:c r="G14" s="20" t="n">
         <x:v>35000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1534,188 +1868,189 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>撤离点ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>X（毫米）</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>Y（毫米）</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>区域宽（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="16" t="str">
         <x:v>区域高（毫米）</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="16" t="str">
         <x:v>撤离读条（Tick）</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="16" t="str">
         <x:v>所需Boss出生ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="G2" s="11" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="H2" s="11" t="str">
+      <x:c r="A2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="G2" s="21" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="H2" s="21" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="13" t="str">
+      <x:c r="A3" s="22" t="str">
         <x:v>ExtractIdx</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="22" t="str">
         <x:v>MapIdx</x:v>
       </x:c>
-      <x:c r="C3" s="13" t="str">
+      <x:c r="C3" s="22" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="D3" s="13" t="str">
+      <x:c r="D3" s="22" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="str">
+      <x:c r="E3" s="22" t="str">
         <x:v>W</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="str">
+      <x:c r="F3" s="22" t="str">
         <x:v>H</x:v>
       </x:c>
-      <x:c r="G3" s="13" t="str">
+      <x:c r="G3" s="22" t="str">
         <x:v>HoldTicks</x:v>
       </x:c>
-      <x:c r="H3" s="13" t="str">
+      <x:c r="H3" s="22" t="str">
         <x:v>NeedBossSpawnIdx</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="15" t="str">
+      <x:c r="A4" s="23" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="15" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="H4" s="15" t="str">
+      <x:c r="B4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="G4" s="23" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="H4" s="23" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
-      <x:c r="A5" s="7" t="n">
+      <x:c r="A5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="n">
+      <x:c r="B5" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="n">
+      <x:c r="C5" s="18" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="n">
+      <x:c r="D5" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="n">
+      <x:c r="E5" s="18" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="n">
+      <x:c r="F5" s="18" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="n">
+      <x:c r="G5" s="18" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H5" s="7" t="n">
+      <x:c r="H5" s="18" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
-      <x:c r="A6" s="8" t="n">
+      <x:c r="A6" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="n">
+      <x:c r="B6" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="n">
         <x:v>14000</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="n">
+      <x:c r="D6" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="n">
+      <x:c r="E6" s="20" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="n">
+      <x:c r="F6" s="20" t="n">
         <x:v>2400</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="n">
+      <x:c r="G6" s="20" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H6" s="8" t="n">
+      <x:c r="H6" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
-      <x:c r="A7" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="n">
+      <x:c r="A7" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="n">
         <x:v>34200</x:v>
       </x:c>
-      <x:c r="D7" s="7" t="n">
+      <x:c r="D7" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E7" s="7" t="n">
+      <x:c r="E7" s="18" t="n">
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="F7" s="7" t="n">
+      <x:c r="F7" s="18" t="n">
         <x:v>2800</x:v>
       </x:c>
-      <x:c r="G7" s="7" t="n">
+      <x:c r="G7" s="18" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H7" s="7" t="n">
+      <x:c r="H7" s="18" t="n">
         <x:v>25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>